--- a/TESTER/TUAN5/test case và báo cáo lỗi.xlsx
+++ b/TESTER/TUAN5/test case và báo cáo lỗi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TESTER\DangVanKhoa\TESTER\TUAN5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB794A3-AE0F-4CDD-9F01-08566C9013E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F7A70A-3107-4D3E-B60F-8E71B0625EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{30CE442A-FBA3-454E-BA71-8B54271EEBE4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{30CE442A-FBA3-454E-BA71-8B54271EEBE4}"/>
   </bookViews>
   <sheets>
     <sheet name="test case bài 4" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="207">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -486,9 +486,6 @@
     <t>50 euro</t>
   </si>
   <si>
-    <t>Child age must be 0–17</t>
-  </si>
-  <si>
     <t>Adult age must be 18–145</t>
   </si>
   <si>
@@ -658,6 +655,12 @@
   </si>
   <si>
     <t>plus(2147483647,1)</t>
+  </si>
+  <si>
+    <t>51 euro</t>
+  </si>
+  <si>
+    <t>81 euro</t>
   </si>
 </sst>
 </file>
@@ -1703,10 +1706,10 @@
         <v>38</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G32" s="5"/>
     </row>
@@ -1724,7 +1727,7 @@
         <v>41</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>145</v>
@@ -1745,7 +1748,7 @@
         <v>47</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>145</v>
@@ -1766,7 +1769,7 @@
         <v>47</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>145</v>
@@ -1787,7 +1790,7 @@
         <v>50</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>145</v>
@@ -1808,7 +1811,7 @@
         <v>50</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>145</v>
@@ -1829,7 +1832,7 @@
         <v>53</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>145</v>
@@ -1850,7 +1853,7 @@
         <v>53</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>145</v>
@@ -1871,7 +1874,7 @@
         <v>41</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>145</v>
@@ -1892,7 +1895,7 @@
         <v>56</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>145</v>
@@ -1913,7 +1916,7 @@
         <v>56</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>145</v>
@@ -1934,10 +1937,10 @@
         <v>59</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G43" s="5"/>
     </row>
@@ -1955,7 +1958,7 @@
         <v>59</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>145</v>
@@ -1976,7 +1979,7 @@
         <v>53</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>145</v>
@@ -1997,7 +2000,7 @@
         <v>53</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>145</v>
@@ -2101,7 +2104,7 @@
         <v>126</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2177,7 +2180,7 @@
         <v>7</v>
       </c>
       <c r="E9" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="24">
         <v>0</v>
@@ -2192,7 +2195,7 @@
         <v>7</v>
       </c>
       <c r="J9" s="26">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2209,7 +2212,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="24">
         <v>0</v>
@@ -2224,7 +2227,7 @@
         <v>14</v>
       </c>
       <c r="J10" s="26">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2238,7 +2241,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="28">
         <v>0</v>
@@ -2252,8 +2255,8 @@
       <c r="I12" s="28">
         <v>21</v>
       </c>
-      <c r="J12" s="29">
-        <v>1</v>
+      <c r="J12" s="26">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -2285,13 +2288,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="32" t="s">
@@ -2329,7 +2332,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>2</v>
@@ -2359,7 +2362,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="34"/>
       <c r="C6" s="34"/>
@@ -2390,13 +2393,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="D8" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -2407,13 +2410,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>173</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -2424,13 +2427,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>175</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -2441,13 +2444,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>177</v>
-      </c>
       <c r="D11" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -2458,13 +2461,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>180</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -2475,13 +2478,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -2492,13 +2495,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>162</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -2509,13 +2512,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -2526,13 +2529,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -2575,7 +2578,7 @@
         <v>13</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" s="35" t="s">
         <v>14</v>
@@ -2587,7 +2590,7 @@
         <v>63</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2595,16 +2598,16 @@
         <v>16</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>194</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F21" s="33" t="s">
         <v>145</v>
@@ -2616,16 +2619,16 @@
         <v>17</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>197</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F22" s="33" t="s">
         <v>145</v>
@@ -2637,19 +2640,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D23" s="8">
         <v>1</v>
       </c>
       <c r="E23" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G23" s="8"/>
     </row>
@@ -2658,10 +2661,10 @@
         <v>19</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D24" s="8">
         <v>120</v>
@@ -2679,16 +2682,16 @@
         <v>20</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F25" s="33" t="s">
         <v>145</v>
@@ -2700,10 +2703,10 @@
         <v>74</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" s="8">
         <v>3</v>
@@ -2715,7 +2718,7 @@
         <v>136</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2723,10 +2726,10 @@
         <v>77</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="D27" s="8">
         <v>2147483648</v>
@@ -2765,7 +2768,7 @@
         <v>122</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>124</v>
@@ -2793,7 +2796,7 @@
         <v>126</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2862,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C9" s="24">
         <v>4</v>
@@ -2871,7 +2874,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="24">
         <v>0</v>
@@ -2886,7 +2889,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="26">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2900,7 +2903,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="28">
         <v>0</v>
@@ -2915,7 +2918,7 @@
         <v>4</v>
       </c>
       <c r="J11" s="29">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
